--- a/Assets/Data/Classic-Repair-Toolbox.xlsx
+++ b/Assets/Data/Classic-Repair-Toolbox.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Development\Visual Studio\Classic-Repair-Toolbox\Assets\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772BAF2C-5B04-419D-9DB5-D732CBD208AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C002A60-3FC7-4AD6-B526-7EE8B763550C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hardware &amp; Board" sheetId="1" r:id="rId1"/>
-    <sheet name="Version match" sheetId="2" r:id="rId2"/>
+    <sheet name="Oscilloscope" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="155">
   <si>
     <t>Hardware name in drop-down</t>
   </si>
@@ -108,15 +108,6 @@
 Has 6581 SID.</t>
   </si>
   <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>CRT version(s) where this Excel will work</t>
-  </si>
-  <si>
-    <t>2025-December-20</t>
-  </si>
-  <si>
     <t>Has 6581 SID</t>
   </si>
   <si>
@@ -147,18 +138,12 @@
     <t>250466 (long board)</t>
   </si>
   <si>
-    <t>2026-February-12</t>
-  </si>
-  <si>
     <t>Has 6581 SID. C128D is with the plastic case</t>
   </si>
   <si>
     <t>Has 8580 SID. This is with the metal case</t>
   </si>
   <si>
-    <t>2026-February-21</t>
-  </si>
-  <si>
     <t>Amstrad CPC 664</t>
   </si>
   <si>
@@ -166,6 +151,366 @@
   </si>
   <si>
     <t>Amstrad CPC 664/MC0005A/Data CPC 664 MC0005A.xlsx</t>
+  </si>
+  <si>
+    <t>PT NO Z70205 MC0005A</t>
+  </si>
+  <si>
+    <t># Oscilloscope configurations</t>
+  </si>
+  <si>
+    <t>Oscilloscope series or specific models</t>
+  </si>
+  <si>
+    <t>SHS1000X</t>
+  </si>
+  <si>
+    <t>Siglent</t>
+  </si>
+  <si>
+    <t>Series or model</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>SDS800X HD</t>
+  </si>
+  <si>
+    <t>SDS1000CML+</t>
+  </si>
+  <si>
+    <t>SDS1000CNL+</t>
+  </si>
+  <si>
+    <t>SDS1000DL+</t>
+  </si>
+  <si>
+    <t>SDS1000X</t>
+  </si>
+  <si>
+    <t>SDS1000X+</t>
+  </si>
+  <si>
+    <t>SDS1000X-E</t>
+  </si>
+  <si>
+    <t>SDS1000X HD</t>
+  </si>
+  <si>
+    <t>SDS1202X-E</t>
+  </si>
+  <si>
+    <t>SDS2000X</t>
+  </si>
+  <si>
+    <t>SDS2000X HD</t>
+  </si>
+  <si>
+    <t>SDS2000X Plus</t>
+  </si>
+  <si>
+    <t>SDS3000X HD</t>
+  </si>
+  <si>
+    <t>SDS5000X</t>
+  </si>
+  <si>
+    <t>SDS6000 Pro</t>
+  </si>
+  <si>
+    <t>SDS6000A</t>
+  </si>
+  <si>
+    <t>SDS6000L</t>
+  </si>
+  <si>
+    <t>SDS7000A</t>
+  </si>
+  <si>
+    <t>SHS800X</t>
+  </si>
+  <si>
+    <t>Identify</t>
+  </si>
+  <si>
+    <t>DrainErrorQueue</t>
+  </si>
+  <si>
+    <t>QueryTriggerLevel</t>
+  </si>
+  <si>
+    <t>QueryActiveTrigger</t>
+  </si>
+  <si>
+    <t>Stop</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>QueryTriggerMode</t>
+  </si>
+  <si>
+    <t>SetTriggerLevel</t>
+  </si>
+  <si>
+    <t>QueryTimeDiv</t>
+  </si>
+  <si>
+    <t>SetTimeDiv</t>
+  </si>
+  <si>
+    <t>QueryVoltsDiv</t>
+  </si>
+  <si>
+    <t>SetVoltsDiv</t>
+  </si>
+  <si>
+    <t>DumpImage</t>
+  </si>
+  <si>
+    <t>*IDN?</t>
+  </si>
+  <si>
+    <t>:SYST:ERR?</t>
+  </si>
+  <si>
+    <t>*OPC?</t>
+  </si>
+  <si>
+    <t>*CLS</t>
+  </si>
+  <si>
+    <t>TRIG_MODE?</t>
+  </si>
+  <si>
+    <t>STOP</t>
+  </si>
+  <si>
+    <t>TRIG_MODE SINGLE</t>
+  </si>
+  <si>
+    <t>TRIG_MODE AUTO</t>
+  </si>
+  <si>
+    <t>TRIG_SELECT?</t>
+  </si>
+  <si>
+    <t>TRIG_LEVEL?</t>
+  </si>
+  <si>
+    <t>C1:TRIG_LEVEL {0}</t>
+  </si>
+  <si>
+    <t>TIME_DIV?</t>
+  </si>
+  <si>
+    <t>TIME_DIV {0}</t>
+  </si>
+  <si>
+    <t>:CHANNEL1:SCALE?</t>
+  </si>
+  <si>
+    <t>:CHANNEL1:SCALE {0}</t>
+  </si>
+  <si>
+    <t>SCDP</t>
+  </si>
+  <si>
+    <t>C1:VOLT_DIV?</t>
+  </si>
+  <si>
+    <t>C1:VOLT_DIV {0}</t>
+  </si>
+  <si>
+    <t>Rigol</t>
+  </si>
+  <si>
+    <t>MSO2000A</t>
+  </si>
+  <si>
+    <t>DHO1000</t>
+  </si>
+  <si>
+    <t>DHO4000</t>
+  </si>
+  <si>
+    <t>DS1000Z</t>
+  </si>
+  <si>
+    <t>DS2000A</t>
+  </si>
+  <si>
+    <t>MSO1000Z</t>
+  </si>
+  <si>
+    <t>1nS,2nS,5nS,10nS,20nS,50nS,100nS,200nS,500nS,1uS,2uS,5uS,10uS,20uS,50uS,100uS,200uS,500uS,1mS,2mS,5mS,10mS,20mS,50mS,100mS,200mS,500mS,1S,2S,5S,10S,20S,50S</t>
+  </si>
+  <si>
+    <t>2mV,5mV,10mV,20mV,50mV,100mV,200mV,500mV,1V,2V,5V,10V</t>
+  </si>
+  <si>
+    <t>TIME/DIV</t>
+  </si>
+  <si>
+    <t>VOLTS/DIV</t>
+  </si>
+  <si>
+    <t>2nS,5nS,10nS,20nS,50nS,100nS,200nS,500nS,1uS,2uS,5uS,10uS,20uS,50uS,100uS,200uS,500uS,1mS,2mS,5mS,10mS,20mS,50mS,100mS,200mS,500mS,1S,2S,5S,10S,20S,50S,100S,200S,500S,1000S</t>
+  </si>
+  <si>
+    <t>5mV,10mV,20mV,50mV,100mV,200mV,500mV,1V,2V,5V,10V,20V,50V,100V</t>
+  </si>
+  <si>
+    <t>TRIGGER:EDGE:LEVEL?</t>
+  </si>
+  <si>
+    <t>TRIGGER:EDGE:LEVEL {0}</t>
+  </si>
+  <si>
+    <t>TIMEBASE:SCALE?</t>
+  </si>
+  <si>
+    <t>TIMEBASE:SCALE {0}</t>
+  </si>
+  <si>
+    <t>CHANNEL1:SCALE?</t>
+  </si>
+  <si>
+    <t>CHANNEL1:SCALE {0}</t>
+  </si>
+  <si>
+    <t>:PRINT? PNG</t>
+  </si>
+  <si>
+    <t>:SYSTEM:ERROR?</t>
+  </si>
+  <si>
+    <t>:CLEAR</t>
+  </si>
+  <si>
+    <t>:TRIGGER:STATUS?</t>
+  </si>
+  <si>
+    <t>:STOP</t>
+  </si>
+  <si>
+    <t>:SINGLE</t>
+  </si>
+  <si>
+    <t>:RUN</t>
+  </si>
+  <si>
+    <t>:TRIGGER:MODE?</t>
+  </si>
+  <si>
+    <t>:TRIGGER:EDGE:LEVEL?</t>
+  </si>
+  <si>
+    <t>:TRIGGER:EDGE:LEVEL {0}</t>
+  </si>
+  <si>
+    <t>:TIMEBASE:SCALE?</t>
+  </si>
+  <si>
+    <t>:TIMEBASE:SCALE {0}</t>
+  </si>
+  <si>
+    <t>:DISPLAY:DATA?</t>
+  </si>
+  <si>
+    <t>Operation-Complete</t>
+  </si>
+  <si>
+    <t>Clear-Statistics</t>
+  </si>
+  <si>
+    <t>Port</t>
+  </si>
+  <si>
+    <t>Debounce-Time</t>
+  </si>
+  <si>
+    <t>100ms</t>
+  </si>
+  <si>
+    <t>Keysight</t>
+  </si>
+  <si>
+    <t>InfiniiVision 2000 X</t>
+  </si>
+  <si>
+    <t>:TRIGGER:LEVEL?</t>
+  </si>
+  <si>
+    <t>:TRIGGER:LEVEL {0}</t>
+  </si>
+  <si>
+    <t>5ns,10ns,20ns,50ns,100ns,200ns,500ns,1us,2us,5us,10us,20us,50us,100us,200us,500us,1ms,2ms,5ms,10ms,20ms,50ms,100ms,200ms,500ms,1s,2s,5s,10s,20s,50s</t>
+  </si>
+  <si>
+    <t>0.5,1,2</t>
+  </si>
+  <si>
+    <t>InfiniiVision 6000 X</t>
+  </si>
+  <si>
+    <t>InfiniiVision 6000L</t>
+  </si>
+  <si>
+    <t>:TRIGGER:SWEEP?</t>
+  </si>
+  <si>
+    <t>:DISPLAY:DATA? PNG</t>
+  </si>
+  <si>
+    <t>Rohde &amp; Schwarz</t>
+  </si>
+  <si>
+    <t>MXO 4</t>
+  </si>
+  <si>
+    <t>RTA4000</t>
+  </si>
+  <si>
+    <t>SYSTEM:ERROR?</t>
+  </si>
+  <si>
+    <t>MEASUREMENT:STATISTICS:RESET</t>
+  </si>
+  <si>
+    <t>TRIGGER:MODE?</t>
+  </si>
+  <si>
+    <t>TRIGGER:LEVEL?</t>
+  </si>
+  <si>
+    <t>TRIGGER:LEVEL {0}</t>
+  </si>
+  <si>
+    <t>HCOPY:DATA?</t>
+  </si>
+  <si>
+    <t>:ACQUIRE:STATE?</t>
+  </si>
+  <si>
+    <t>SINGLE</t>
+  </si>
+  <si>
+    <t>RUN</t>
+  </si>
+  <si>
+    <t>TRIGGER:A:MODE?</t>
+  </si>
+  <si>
+    <t>TRIGGER:A:LEVEL?</t>
+  </si>
+  <si>
+    <t>TRIGGER:A:LEVEL {0} 1</t>
   </si>
   <si>
     <r>
@@ -180,18 +525,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-March-2</t>
+      <t>2026-March-30</t>
     </r>
-  </si>
-  <si>
-    <t>PT NO Z70205 MC0005A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,6 +592,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFA31515"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -284,7 +645,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -321,6 +682,22 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -643,8 +1020,8 @@
   <cols>
     <col min="1" max="1" width="35.44140625" style="5" customWidth="1"/>
     <col min="2" max="2" width="29.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="51.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="52.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="77.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="32.109375" style="1" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
@@ -661,7 +1038,7 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -698,16 +1075,16 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -726,13 +1103,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -740,13 +1117,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -754,7 +1131,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
@@ -768,41 +1145,41 @@
         <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -948,61 +1325,2448 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56206CAE-0631-4609-AB22-50D6669B86E2}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:AF39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="85.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="17" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" style="14" customWidth="1"/>
+    <col min="8" max="8" width="30.21875" style="14" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" style="14" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="14" customWidth="1"/>
+    <col min="11" max="11" width="19.77734375" style="14" customWidth="1"/>
+    <col min="12" max="12" width="17.44140625" style="14" customWidth="1"/>
+    <col min="13" max="13" width="17.77734375" style="14" customWidth="1"/>
+    <col min="14" max="14" width="23" style="14" customWidth="1"/>
+    <col min="15" max="15" width="25.44140625" style="14" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" style="14" customWidth="1"/>
+    <col min="17" max="17" width="21.33203125" style="14" customWidth="1"/>
+    <col min="18" max="18" width="21.109375" style="14" customWidth="1"/>
+    <col min="19" max="19" width="22.33203125" style="14" customWidth="1"/>
+    <col min="20" max="20" width="21.109375" style="14" customWidth="1"/>
+    <col min="21" max="21" width="34.88671875" style="14" customWidth="1"/>
+    <col min="22" max="22" width="64.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="32" width="8.88671875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+    </row>
+    <row r="2" spans="1:32" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13"/>
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="13"/>
+    </row>
+    <row r="3" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
-    </row>
-    <row r="4" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="13"/>
+      <c r="AF3" s="13"/>
+    </row>
+    <row r="4" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="13"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="13"/>
+      <c r="AF4" s="13"/>
+    </row>
+    <row r="5" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="13"/>
+      <c r="AE5" s="13"/>
+      <c r="AF5" s="13"/>
+    </row>
+    <row r="6" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-    </row>
-    <row r="7" spans="1:1" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="13"/>
+      <c r="AF6" s="13"/>
+    </row>
+    <row r="7" spans="1:32" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+    </row>
+    <row r="8" spans="1:32" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="R8" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="T8" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="U8" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="V8" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="13"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="B9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9">
+        <v>5025</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="M9" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q9" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="V9" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="B10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10">
+        <v>5025</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="P10" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q10" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R10" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T10" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="V10" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>129</v>
+      </c>
+      <c r="B11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11">
+        <v>5025</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R11" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T11" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="V11" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12">
+        <v>5555</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="O12" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q12" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R12" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S12" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T12" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="U12" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="V12" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13">
+        <v>5555</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="O13" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q13" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R13" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T13" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="U13" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="V13" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14">
+        <v>5555</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="N14" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q14" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R14" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T14" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="U14" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="V14" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15">
+        <v>5555</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="N15" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="P15" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q15" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R15" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S15" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T15" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="U15" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="V15" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16">
+        <v>5555</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="O16" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="P16" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q16" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R16" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S16" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T16" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="U16" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="V16" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17">
+        <v>5555</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q17" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S17" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T17" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="U17" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="V17" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18">
+        <v>5025</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="N18" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="P18" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q18" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R18" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S18" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T18" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="U18" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="V18" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19">
+        <v>5025</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="N19" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="P19" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q19" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R19" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S19" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T19" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="U19" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="V19" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20">
+        <v>5025</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N20" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P20" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q20" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R20" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S20" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T20" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U20" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V20" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21">
+        <v>5025</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N21" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="O21" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="P21" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q21" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R21" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S21" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T21" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U21" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V21" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22">
+        <v>5025</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="P22" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q22" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R22" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S22" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T22" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U22" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V22" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23">
+        <v>5025</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J23" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N23" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q23" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R23" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S23" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T23" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U23" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V23" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24">
+        <v>5025</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N24" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="P24" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q24" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R24" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S24" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T24" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U24" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V24" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25">
+        <v>5025</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N25" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="O25" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="P25" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q25" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R25" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S25" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T25" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U25" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V25" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26">
+        <v>5025</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N26" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="O26" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="P26" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q26" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R26" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S26" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T26" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U26" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V26" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27">
+        <v>5025</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O27" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P27" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q27" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R27" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S27" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T27" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U27" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V27" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28">
+        <v>5025</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N28" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="P28" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q28" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R28" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="S28" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="T28" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U28" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V28" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29">
+        <v>5025</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L29" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N29" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="P29" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q29" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R29" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="S29" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="T29" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="U29" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V29" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30">
+        <v>5025</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L30" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M30" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N30" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O30" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P30" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q30" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R30" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S30" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T30" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U30" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V30" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31">
+        <v>5025</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M31" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N31" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O31" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P31" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q31" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R31" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S31" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T31" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U31" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V31" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32">
+        <v>5025</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M32" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O32" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P32" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q32" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R32" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S32" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T32" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U32" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V32" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33">
+        <v>5025</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N33" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O33" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P33" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q33" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R33" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S33" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T33" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U33" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V33" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34">
+        <v>5025</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L34" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M34" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N34" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O34" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P34" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q34" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R34" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S34" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T34" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U34" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V34" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35">
+        <v>5025</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N35" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O35" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P35" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q35" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R35" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S35" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T35" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U35" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V35" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36">
+        <v>5025</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M36" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N36" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O36" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P36" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q36" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R36" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S36" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T36" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U36" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V36" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37">
+        <v>5025</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M37" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N37" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O37" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P37" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q37" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R37" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S37" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T37" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U37" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V37" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38">
+        <v>5025</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L38" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N38" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O38" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P38" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q38" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R38" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S38" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T38" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U38" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V38" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39">
+        <v>5025</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M39" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="N39" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="O39" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P39" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q39" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="R39" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="S39" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T39" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="U39" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="V39" s="14" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
